--- a/artfynd/A 3329-2021 artfynd.xlsx
+++ b/artfynd/A 3329-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3329-2021 artfynd.xlsx
+++ b/artfynd/A 3329-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2334,6 +2334,134 @@
           <t>Alight - NVI Hasslösa Solcellspark</t>
         </is>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125371962</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57608</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sandtorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>399995</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6476271</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hasslösa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Kindgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Kindgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3329-2021 artfynd.xlsx
+++ b/artfynd/A 3329-2021 artfynd.xlsx
@@ -2340,7 +2340,7 @@
         <v>125371962</v>
       </c>
       <c r="B17" t="n">
-        <v>57608</v>
+        <v>57722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 3329-2021 artfynd.xlsx
+++ b/artfynd/A 3329-2021 artfynd.xlsx
@@ -2340,12 +2340,7 @@
         <v>125371962</v>
       </c>
       <c r="B17" t="n">
-        <v>57722</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
